--- a/events/London_2012_OG/London_2012_OG_Results.xlsx
+++ b/events/London_2012_OG/London_2012_OG_Results.xlsx
@@ -732,6 +732,11 @@
           <t>3:30.852</t>
         </is>
       </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>43679</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1162,6 +1167,11 @@
           <t>3:36.012</t>
         </is>
       </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2432,6 +2442,11 @@
           <t>3:29.825</t>
         </is>
       </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2617,6 +2632,11 @@
           <t>3:31.937</t>
         </is>
       </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>43679</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3132,6 +3152,11 @@
           <t>3:32.396</t>
         </is>
       </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3323,6 +3348,11 @@
           <t>3:29.938</t>
         </is>
       </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>43679</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3977,6 +4007,11 @@
           <t>4:04.109</t>
         </is>
       </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>36159</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5547,6 +5582,11 @@
           <t>3:53.305</t>
         </is>
       </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>36159</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6373,6 +6413,11 @@
           <t>3:51.535</t>
         </is>
       </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>36159</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -7009,6 +7054,11 @@
           <t>3:19.073</t>
         </is>
       </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -7809,6 +7859,11 @@
           <t>3:13.239</t>
         </is>
       </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -8632,6 +8687,11 @@
           <t>3:11.456</t>
         </is>
       </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -9323,6 +9383,11 @@
           <t>1:37.355</t>
         </is>
       </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>36222</t>
+        </is>
+      </c>
       <c r="S137" t="inlineStr">
         <is>
           <t>35813</t>
@@ -9818,6 +9883,11 @@
           <t>42059</t>
         </is>
       </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -9883,6 +9953,11 @@
           <t>36170</t>
         </is>
       </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>36164</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -10088,6 +10163,11 @@
           <t>42059</t>
         </is>
       </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -10153,6 +10233,11 @@
           <t>36170</t>
         </is>
       </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>36164</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -10213,6 +10298,11 @@
           <t>1:32.550</t>
         </is>
       </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>36222</t>
+        </is>
+      </c>
       <c r="S150" t="inlineStr">
         <is>
           <t>35813</t>
@@ -10709,6 +10799,11 @@
           <t>42059</t>
         </is>
       </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -10843,6 +10938,11 @@
           <t>1:33.055</t>
         </is>
       </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>36222</t>
+        </is>
+      </c>
       <c r="S159" t="inlineStr">
         <is>
           <t>35813</t>
@@ -11002,6 +11102,11 @@
           <t>36170</t>
         </is>
       </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>36164</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -13053,6 +13158,16 @@
           <t>3:37.568</t>
         </is>
       </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>36161</t>
+        </is>
+      </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>36160</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -13713,6 +13828,16 @@
           <t>3:36.456</t>
         </is>
       </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>36161</t>
+        </is>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>36160</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -14454,6 +14579,16 @@
           <t>3:36.414</t>
         </is>
       </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>36161</t>
+        </is>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>36160</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -19858,6 +19993,11 @@
           <t>1:44.568</t>
         </is>
       </c>
+      <c r="R294" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -20643,6 +20783,11 @@
           <t>1:43.152</t>
         </is>
       </c>
+      <c r="R306" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -21976,6 +22121,11 @@
           <t>1:44.407</t>
         </is>
       </c>
+      <c r="R326" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -23135,6 +23285,11 @@
           <t>0:36.560</t>
         </is>
       </c>
+      <c r="R344" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -24465,6 +24620,11 @@
           <t>0:37.660</t>
         </is>
       </c>
+      <c r="R365" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -25316,6 +25476,11 @@
           <t>0:39.370</t>
         </is>
       </c>
+      <c r="R378" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -25893,6 +26058,11 @@
           <t>0:41.378</t>
         </is>
       </c>
+      <c r="R387" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -27533,6 +27703,11 @@
           <t>0:40.346</t>
         </is>
       </c>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -28669,6 +28844,11 @@
           <t>0:42.853</t>
         </is>
       </c>
+      <c r="R431" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -30295,6 +30475,11 @@
           <t>0:42.388</t>
         </is>
       </c>
+      <c r="R456" t="inlineStr">
+        <is>
+          <t>36222</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -31995,6 +32180,11 @@
           <t>0:41.734</t>
         </is>
       </c>
+      <c r="R483" t="inlineStr">
+        <is>
+          <t>36222</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -33284,6 +33474,11 @@
           <t>0:46.161</t>
         </is>
       </c>
+      <c r="R503" t="inlineStr">
+        <is>
+          <t>36222</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -34471,6 +34666,11 @@
           <t>36228</t>
         </is>
       </c>
+      <c r="S521" t="inlineStr">
+        <is>
+          <t>36229</t>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -34531,6 +34731,11 @@
           <t>0:33.623</t>
         </is>
       </c>
+      <c r="R522" t="inlineStr">
+        <is>
+          <t>42725</t>
+        </is>
+      </c>
       <c r="S522" t="inlineStr">
         <is>
           <t>42726</t>
@@ -34936,6 +35141,11 @@
           <t>36228</t>
         </is>
       </c>
+      <c r="S528" t="inlineStr">
+        <is>
+          <t>36229</t>
+        </is>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -34996,6 +35206,11 @@
           <t>0:33.105</t>
         </is>
       </c>
+      <c r="R529" t="inlineStr">
+        <is>
+          <t>42725</t>
+        </is>
+      </c>
       <c r="S529" t="inlineStr">
         <is>
           <t>42726</t>
@@ -35617,6 +35832,11 @@
           <t>36228</t>
         </is>
       </c>
+      <c r="S538" t="inlineStr">
+        <is>
+          <t>36229</t>
+        </is>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -35749,6 +35969,11 @@
       <c r="P540" t="inlineStr">
         <is>
           <t>0:35.271</t>
+        </is>
+      </c>
+      <c r="R540" t="inlineStr">
+        <is>
+          <t>42725</t>
         </is>
       </c>
       <c r="S540" t="inlineStr">
@@ -36324,7 +36549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D151"/>
+  <dimension ref="A1:D164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39649,6 +39874,292 @@
         </is>
       </c>
     </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Ivan</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>SHTYL</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>36159</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Ilia</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>SHTOKALOV</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>36160</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Ilya</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>PERVUKHIN</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>36161</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Alexey</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>KOROVASHKOV</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>36164</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Natalia</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>PODOLSKAIA</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>36222</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Jessica</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>WALKER</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>36229</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Jonathan</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>SCHOFIELD</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Aleh</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>YURENIA</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Volha</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>KHUDZENKA</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Kenny</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>WALLACE</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Timothy</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>HORNSBY</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>42725</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Miguel</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>CORREA</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>43679</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Jorge A</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>GARCIA RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/London_2012_OG/London_2012_OG_Results.xlsx
+++ b/events/London_2012_OG/London_2012_OG_Results.xlsx
@@ -26818,6 +26818,11 @@
           <t>0:41.036</t>
         </is>
       </c>
+      <c r="R399" t="inlineStr">
+        <is>
+          <t>46354</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -28208,6 +28213,11 @@
           <t>0:40.647</t>
         </is>
       </c>
+      <c r="R421" t="inlineStr">
+        <is>
+          <t>46354</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -28713,6 +28723,11 @@
       <c r="P429" t="inlineStr">
         <is>
           <t>0:42.291</t>
+        </is>
+      </c>
+      <c r="R429" t="inlineStr">
+        <is>
+          <t>46354</t>
         </is>
       </c>
     </row>
@@ -36549,7 +36564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D164"/>
+  <dimension ref="A1:D165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40160,6 +40175,28 @@
         </is>
       </c>
     </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>46354</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Yuri</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>CHEBAN</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
